--- a/output/pdf_financials_xlsx/COCO.xlsx
+++ b/output/pdf_financials_xlsx/COCO.xlsx
@@ -1192,7 +1192,7 @@
         <v>-0.01</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.022324</v>
+        <v>-0.022324</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.027281</v>
@@ -1460,7 +1460,7 @@
         <v>-0.01</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.022324</v>
+        <v>-0.022324</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.027281</v>
@@ -1616,7 +1616,7 @@
         <v>-0.01</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.022324</v>
+        <v>-0.022324</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.027281</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.5581</v>
+        <v>0.5581</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>-0.01</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.022324</v>
+        <v>-0.022324</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.027281</v>
@@ -1938,7 +1938,7 @@
         <v>-0.01</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.022324</v>
+        <v>-0.022324</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.027281</v>
@@ -2072,7 +2072,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -5392,7 +5392,7 @@
         <v>0.006</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -13979,7 +13979,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -47320,10 +47324,10 @@
         </is>
       </c>
       <c r="F442" s="5" t="n">
-        <v>0.022324</v>
+        <v>-0.022324</v>
       </c>
       <c r="G442" s="5" t="n">
-        <v>0.027281</v>
+        <v>-0.027281</v>
       </c>
       <c r="H442" t="inlineStr">
         <is>
@@ -48686,10 +48690,10 @@
         </is>
       </c>
       <c r="E457" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F457" s="5" t="n">
-        <v>0.022324</v>
+        <v>-0.022324</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/COCO.xlsx
+++ b/output/pdf_financials_xlsx/COCO.xlsx
@@ -990,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006481</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006731</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001327</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001168</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1008,22 +1008,22 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000669</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002855</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002985</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002749</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002737</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006671</v>
       </c>
     </row>
     <row r="13">
@@ -1800,28 +1800,22 @@
         <v>14.7572</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>30.864</v>
+        <v>30.778291</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>42.692233</v>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>42.452348</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>57.591142</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>48.60065</v>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>64.22306</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>70.966854</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>74.71169</v>
       </c>
     </row>
     <row r="27">
@@ -1840,16 +1834,16 @@
         <v>-0.027281</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.026459</v>
+        <v>-2.019978</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.6160099999999999</v>
+        <v>-0.609279</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.5301709999999999</v>
+        <v>-0.528844</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.712681</v>
+        <v>-0.711513</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.735083</v>
@@ -1858,22 +1852,22 @@
         <v>-0.295144</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.92592</v>
+        <v>-0.925251</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.280767</v>
+        <v>-1.277912</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.972013</v>
+        <v>-0.969028</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.972013</v>
+        <v>-0.969264</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.436665</v>
+        <v>-0.433928</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.436665</v>
+        <v>-0.429994</v>
       </c>
     </row>
     <row r="28">
@@ -1944,16 +1938,16 @@
         <v>-0.027281</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.026459</v>
+        <v>-2.019978</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.6160099999999999</v>
+        <v>-0.609279</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.5301709999999999</v>
+        <v>-0.528844</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.712681</v>
+        <v>-0.711513</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.735083</v>
@@ -1962,22 +1956,22 @@
         <v>-0.295144</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.92592</v>
+        <v>-0.925251</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.280767</v>
+        <v>-1.277912</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.972013</v>
+        <v>-0.969028</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.972013</v>
+        <v>-0.969264</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.436665</v>
+        <v>-0.433928</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.436665</v>
+        <v>-0.429994</v>
       </c>
     </row>
     <row r="30">
@@ -2210,10 +2204,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0944</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.264608</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.241257</v>
@@ -2228,31 +2222,31 @@
         <v>0.476425</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.29471</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.187337</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.15901</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.463598</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.449264</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.080898</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.036727</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.561061</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.835676</v>
       </c>
     </row>
     <row r="35">
@@ -2314,10 +2308,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0944</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.264608</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.241257</v>
@@ -2332,31 +2326,31 @@
         <v>0.476425</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.29471</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.187337</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.15901</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.025</v>
+        <v>1.488598</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.121214</v>
+        <v>1.570478</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.335746</v>
+        <v>0.416644</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.283149</v>
+        <v>0.319876</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.295578</v>
+        <v>0.856639</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.124024</v>
+        <v>1.9597</v>
       </c>
     </row>
     <row r="37">
@@ -2938,10 +2932,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.0944</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.264608</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2956,13 +2950,13 @@
         <v>0.007856999999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.298709</v>
+        <v>0.003999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.187712</v>
+        <v>0.000375</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.15901</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -7817,7 +7811,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8495,7 +8489,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10457,7 +10455,11 @@
           <t>Reclamation deposit 5</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -10823,7 +10825,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -13706,7 +13708,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -20388,7 +20390,11 @@
           <t>Reclamation deposit 5</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -30395,7 +30401,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -31012,7 +31018,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -35045,7 +35051,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -41713,7 +41719,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -44848,7 +44854,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">

--- a/output/pdf_financials_xlsx/COCO.xlsx
+++ b/output/pdf_financials_xlsx/COCO.xlsx
@@ -833,19 +833,19 @@
         <v>0.052278</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.034132</v>
+        <v>0.271859</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.023684</v>
+        <v>0.273687</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.040981</v>
+        <v>0.289716</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.00073</v>
+        <v>0.200904</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.000973</v>
+        <v>0.230826</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0</v>
@@ -885,13 +885,13 @@
         <v>0.081204</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.047949</v>
+        <v>0.285676</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.041741</v>
+        <v>0.291744</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.064192</v>
+        <v>0.312927</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.835083</v>
@@ -937,13 +937,13 @@
         <v>-0.081204</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.047949</v>
+        <v>-0.285676</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.041741</v>
+        <v>-0.291744</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.064192</v>
+        <v>-0.312927</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.196375</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -27066,7 +27066,11 @@
           <t>Proceeds from the issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -40390,7 +40394,11 @@
           <t>Salaries and personnel costs (Note 9)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -42059,7 +42067,11 @@
           <t>Salaries and personnel costs (Note 9)</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/COCO.xlsx
+++ b/output/pdf_financials_xlsx/COCO.xlsx
@@ -723,25 +723,25 @@
         <v>0.009811</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.014767</v>
+        <v>0.014981</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.028926</v>
+        <v>0.045572</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.013817</v>
+        <v>0.046916</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.018057</v>
+        <v>0.048436</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.023211</v>
+        <v>0.053646</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.022894</v>
+        <v>0.039849</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.012648</v>
+        <v>0.026761</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.029581</v>
@@ -879,19 +879,19 @@
         <v>0.009811</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.014767</v>
+        <v>0.014981</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.081204</v>
+        <v>0.09785000000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.285676</v>
+        <v>0.318775</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.291744</v>
+        <v>0.322123</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.312927</v>
+        <v>0.343362</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.835083</v>
@@ -931,19 +931,19 @@
         <v>-0.009811</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.014767</v>
+        <v>-0.014981</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.081204</v>
+        <v>-0.09785000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.285676</v>
+        <v>-0.318775</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.291744</v>
+        <v>-0.322123</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.312927</v>
+        <v>-0.343362</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -40212,7 +40212,11 @@
           <t>Office expenses (Note 9)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -41897,7 +41901,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -45050,7 +45058,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -46235,7 +46247,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
